--- a/Experimenten.xlsx
+++ b/Experimenten.xlsx
@@ -1,26 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stichtingfontys-my.sharepoint.com/personal/582755_student_fontys_nl/Documents/Leerjaar 2/Periode 1/Operations Research 5/OR5/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_2B59D2BFD3B0D2151522C0F050EC68374B47FB5F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{37F27080-95CD-4FD8-9498-322EBC65783E}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_95EC686F11BDBA4E79E2DE4F4CDD18D428DF8E2A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3191706-C65E-43E3-A992-83E92E14118B}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="-90" windowWidth="19380" windowHeight="10260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="t_max" sheetId="1" r:id="rId1"/>
+    <sheet name="cooling_factor" sheetId="2" r:id="rId2"/>
+    <sheet name="cooling_it" sheetId="3" r:id="rId3"/>
+    <sheet name="temp" sheetId="4" r:id="rId4"/>
+    <sheet name="random_seed" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="11">
   <si>
     <t>t_max</t>
   </si>
@@ -50,6 +54,9 @@
   </si>
   <si>
     <t>Totale rekentijd (s)</t>
+  </si>
+  <si>
+    <t>Random seed</t>
   </si>
 </sst>
 </file>
@@ -389,21 +396,973 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:K8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>100</v>
+      </c>
+      <c r="B2">
+        <v>0.99</v>
+      </c>
+      <c r="C2">
+        <v>1000</v>
+      </c>
+      <c r="D2">
+        <v>1000</v>
+      </c>
+      <c r="E2">
+        <v>4182.75</v>
+      </c>
+      <c r="F2">
+        <v>1411.583333333333</v>
+      </c>
+      <c r="G2">
+        <v>157.6944444444444</v>
+      </c>
+      <c r="H2">
+        <v>6.9067000003997236E-3</v>
+      </c>
+      <c r="I2">
+        <v>0.44307800000024139</v>
+      </c>
+      <c r="J2">
+        <v>0.44998470000064122</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>500</v>
+      </c>
+      <c r="B3">
+        <v>0.99</v>
+      </c>
+      <c r="C3">
+        <v>1000</v>
+      </c>
+      <c r="D3">
+        <v>1000</v>
+      </c>
+      <c r="E3">
+        <v>3681.8055555555561</v>
+      </c>
+      <c r="F3">
+        <v>1328.1388888888889</v>
+      </c>
+      <c r="G3">
+        <v>165.19444444444451</v>
+      </c>
+      <c r="H3">
+        <v>2.8737699998600871E-2</v>
+      </c>
+      <c r="I3">
+        <v>0.46587460000046121</v>
+      </c>
+      <c r="J3">
+        <v>0.49461229999906209</v>
+      </c>
+      <c r="K3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>1000</v>
+      </c>
+      <c r="B4">
+        <v>0.99</v>
+      </c>
+      <c r="C4">
+        <v>1000</v>
+      </c>
+      <c r="D4">
+        <v>1000</v>
+      </c>
+      <c r="E4">
+        <v>3681.8055555555561</v>
+      </c>
+      <c r="F4">
+        <v>1328.1388888888889</v>
+      </c>
+      <c r="G4">
+        <v>165.19444444444451</v>
+      </c>
+      <c r="H4">
+        <v>5.7751500000449603E-2</v>
+      </c>
+      <c r="I4">
+        <v>0.45838030000049912</v>
+      </c>
+      <c r="J4">
+        <v>0.51613180000094872</v>
+      </c>
+      <c r="K4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>5000</v>
+      </c>
+      <c r="B5">
+        <v>0.99</v>
+      </c>
+      <c r="C5">
+        <v>1000</v>
+      </c>
+      <c r="D5">
+        <v>1000</v>
+      </c>
+      <c r="E5">
+        <v>3464.166666666667</v>
+      </c>
+      <c r="F5">
+        <v>1145.833333333333</v>
+      </c>
+      <c r="G5">
+        <v>122.3888888888889</v>
+      </c>
+      <c r="H5">
+        <v>0.30579380000017409</v>
+      </c>
+      <c r="I5">
+        <v>0.25224270000035182</v>
+      </c>
+      <c r="J5">
+        <v>0.55803650000052585</v>
+      </c>
+      <c r="K5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>10000</v>
+      </c>
+      <c r="B6">
+        <v>0.99</v>
+      </c>
+      <c r="C6">
+        <v>1000</v>
+      </c>
+      <c r="D6">
+        <v>1000</v>
+      </c>
+      <c r="E6">
+        <v>2963.3611111111109</v>
+      </c>
+      <c r="F6">
+        <v>1001.6666666666659</v>
+      </c>
+      <c r="G6">
+        <v>118.6944444444444</v>
+      </c>
+      <c r="H6">
+        <v>0.61127099999976053</v>
+      </c>
+      <c r="I6">
+        <v>0.40783439999904658</v>
+      </c>
+      <c r="J6">
+        <v>1.0191053999988069</v>
+      </c>
+      <c r="K6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>50000</v>
+      </c>
+      <c r="B7">
+        <v>0.99</v>
+      </c>
+      <c r="C7">
+        <v>1000</v>
+      </c>
+      <c r="D7">
+        <v>1000</v>
+      </c>
+      <c r="E7">
+        <v>2465.0277777777769</v>
+      </c>
+      <c r="F7">
+        <v>1062.1111111111111</v>
+      </c>
+      <c r="G7">
+        <v>137.2777777777778</v>
+      </c>
+      <c r="H7">
+        <v>3.2384328000007372</v>
+      </c>
+      <c r="I7">
+        <v>0.1530184000002919</v>
+      </c>
+      <c r="J7">
+        <v>3.3914512000010291</v>
+      </c>
+      <c r="K7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>1000000</v>
+      </c>
+      <c r="B8">
+        <v>0.99</v>
+      </c>
+      <c r="C8">
+        <v>1000</v>
+      </c>
+      <c r="D8">
+        <v>1000</v>
+      </c>
+      <c r="E8">
+        <v>301.77777777777783</v>
+      </c>
+      <c r="F8">
+        <v>301.77777777777783</v>
+      </c>
+      <c r="G8">
+        <v>47.333333333333343</v>
+      </c>
+      <c r="H8">
+        <v>64.528239699999176</v>
+      </c>
+      <c r="I8">
+        <v>2.1949899999526679E-2</v>
+      </c>
+      <c r="J8">
+        <v>64.550189599998703</v>
+      </c>
+      <c r="K8">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>50000</v>
+      </c>
+      <c r="B2">
+        <v>0.9</v>
+      </c>
+      <c r="C2">
+        <v>1000</v>
+      </c>
+      <c r="D2">
+        <v>1000</v>
+      </c>
+      <c r="E2">
+        <v>362.94444444444429</v>
+      </c>
+      <c r="F2">
+        <v>362.94444444444429</v>
+      </c>
+      <c r="G2">
+        <v>46.583333333333343</v>
+      </c>
+      <c r="H2">
+        <v>3.0861120999998088</v>
+      </c>
+      <c r="I2">
+        <v>2.1692000000257391E-2</v>
+      </c>
+      <c r="J2">
+        <v>3.1078041000000671</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>50000</v>
+      </c>
+      <c r="B3">
+        <v>0.95</v>
+      </c>
+      <c r="C3">
+        <v>1000</v>
+      </c>
+      <c r="D3">
+        <v>1000</v>
+      </c>
+      <c r="E3">
+        <v>938.61111111111154</v>
+      </c>
+      <c r="F3">
+        <v>643.00000000000023</v>
+      </c>
+      <c r="G3">
+        <v>71.250000000000028</v>
+      </c>
+      <c r="H3">
+        <v>3.0884862000002609</v>
+      </c>
+      <c r="I3">
+        <v>8.6445800001456519E-2</v>
+      </c>
+      <c r="J3">
+        <v>3.1749320000017178</v>
+      </c>
+      <c r="K3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>50000</v>
+      </c>
+      <c r="B4">
+        <v>0.97</v>
+      </c>
+      <c r="C4">
+        <v>1000</v>
+      </c>
+      <c r="D4">
+        <v>1000</v>
+      </c>
+      <c r="E4">
+        <v>1589.25</v>
+      </c>
+      <c r="F4">
+        <v>972.4722222222224</v>
+      </c>
+      <c r="G4">
+        <v>89.972222222222243</v>
+      </c>
+      <c r="H4">
+        <v>3.1015975999998768</v>
+      </c>
+      <c r="I4">
+        <v>0.24568579999868231</v>
+      </c>
+      <c r="J4">
+        <v>3.3472833999985601</v>
+      </c>
+      <c r="K4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>50000</v>
+      </c>
+      <c r="B5">
+        <v>0.99</v>
+      </c>
+      <c r="C5">
+        <v>1000</v>
+      </c>
+      <c r="D5">
+        <v>1000</v>
+      </c>
+      <c r="E5">
+        <v>2465.0277777777769</v>
+      </c>
+      <c r="F5">
+        <v>1062.1111111111111</v>
+      </c>
+      <c r="G5">
+        <v>137.2777777777778</v>
+      </c>
+      <c r="H5">
+        <v>3.1226803999998078</v>
+      </c>
+      <c r="I5">
+        <v>0.15142620000005991</v>
+      </c>
+      <c r="J5">
+        <v>3.2741065999998682</v>
+      </c>
+      <c r="K5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>50000</v>
+      </c>
+      <c r="B6">
+        <v>0.995</v>
+      </c>
+      <c r="C6">
+        <v>1000</v>
+      </c>
+      <c r="D6">
+        <v>1000</v>
+      </c>
+      <c r="E6">
+        <v>2004.916666666667</v>
+      </c>
+      <c r="F6">
+        <v>986.00000000000023</v>
+      </c>
+      <c r="G6">
+        <v>103.75</v>
+      </c>
+      <c r="H6">
+        <v>3.0750442999997181</v>
+      </c>
+      <c r="I6">
+        <v>0.19415649999973539</v>
+      </c>
+      <c r="J6">
+        <v>3.269200799999453</v>
+      </c>
+      <c r="K6">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>50000</v>
+      </c>
+      <c r="B2">
+        <v>0.99</v>
+      </c>
+      <c r="C2">
+        <v>100</v>
+      </c>
+      <c r="D2">
+        <v>1000</v>
+      </c>
+      <c r="E2">
+        <v>355.27777777777749</v>
+      </c>
+      <c r="F2">
+        <v>355.27777777777749</v>
+      </c>
+      <c r="G2">
+        <v>49.166666666666643</v>
+      </c>
+      <c r="H2">
+        <v>2.912411799999973</v>
+      </c>
+      <c r="I2">
+        <v>2.0562900001095841E-2</v>
+      </c>
+      <c r="J2">
+        <v>2.932974700001068</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>50000</v>
+      </c>
+      <c r="B3">
+        <v>0.99</v>
+      </c>
+      <c r="C3">
+        <v>250</v>
+      </c>
+      <c r="D3">
+        <v>1000</v>
+      </c>
+      <c r="E3">
+        <v>1291.166666666667</v>
+      </c>
+      <c r="F3">
+        <v>678.8611111111112</v>
+      </c>
+      <c r="G3">
+        <v>88.6111111111111</v>
+      </c>
+      <c r="H3">
+        <v>3.0225955999994771</v>
+      </c>
+      <c r="I3">
+        <v>0.20711110000047481</v>
+      </c>
+      <c r="J3">
+        <v>3.229706699999952</v>
+      </c>
+      <c r="K3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>50000</v>
+      </c>
+      <c r="B4">
+        <v>0.99</v>
+      </c>
+      <c r="C4">
+        <v>500</v>
+      </c>
+      <c r="D4">
+        <v>1000</v>
+      </c>
+      <c r="E4">
+        <v>2308.6944444444439</v>
+      </c>
+      <c r="F4">
+        <v>494.77777777777771</v>
+      </c>
+      <c r="G4">
+        <v>64.916666666666657</v>
+      </c>
+      <c r="H4">
+        <v>3.0387492999998358</v>
+      </c>
+      <c r="I4">
+        <v>0.40901539999867959</v>
+      </c>
+      <c r="J4">
+        <v>3.447764699998515</v>
+      </c>
+      <c r="K4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>50000</v>
+      </c>
+      <c r="B5">
+        <v>0.99</v>
+      </c>
+      <c r="C5">
+        <v>1000</v>
+      </c>
+      <c r="D5">
+        <v>1000</v>
+      </c>
+      <c r="E5">
+        <v>2465.0277777777769</v>
+      </c>
+      <c r="F5">
+        <v>1062.1111111111111</v>
+      </c>
+      <c r="G5">
+        <v>137.2777777777778</v>
+      </c>
+      <c r="H5">
+        <v>3.075875200000155</v>
+      </c>
+      <c r="I5">
+        <v>0.14992600000005041</v>
+      </c>
+      <c r="J5">
+        <v>3.225801200000205</v>
+      </c>
+      <c r="K5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>50000</v>
+      </c>
+      <c r="B6">
+        <v>0.99</v>
+      </c>
+      <c r="C6">
+        <v>2000</v>
+      </c>
+      <c r="D6">
+        <v>1000</v>
+      </c>
+      <c r="E6">
+        <v>2439.8055555555561</v>
+      </c>
+      <c r="F6">
+        <v>880.52777777777783</v>
+      </c>
+      <c r="G6">
+        <v>122.8888888888889</v>
+      </c>
+      <c r="H6">
+        <v>3.0694257000013749</v>
+      </c>
+      <c r="I6">
+        <v>0.30781149999893392</v>
+      </c>
+      <c r="J6">
+        <v>3.3772372000003088</v>
+      </c>
+      <c r="K6">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>50000</v>
+      </c>
+      <c r="B2">
+        <v>0.99</v>
+      </c>
+      <c r="C2">
+        <v>1000</v>
+      </c>
+      <c r="D2">
+        <v>100</v>
+      </c>
+      <c r="E2">
+        <v>532.52777777777771</v>
+      </c>
+      <c r="F2">
+        <v>468.27777777777783</v>
+      </c>
+      <c r="G2">
+        <v>68.1388888888889</v>
+      </c>
+      <c r="H2">
+        <v>2.9739177000010391</v>
+      </c>
+      <c r="I2">
+        <v>0.1029367999999522</v>
+      </c>
+      <c r="J2">
+        <v>3.0768545000009908</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>50000</v>
+      </c>
+      <c r="B3">
+        <v>0.99</v>
+      </c>
+      <c r="C3">
+        <v>1000</v>
+      </c>
+      <c r="D3">
+        <v>250</v>
+      </c>
+      <c r="E3">
+        <v>1069.6944444444439</v>
+      </c>
+      <c r="F3">
+        <v>838.88888888888869</v>
+      </c>
+      <c r="G3">
+        <v>106.9444444444444</v>
+      </c>
+      <c r="H3">
+        <v>2.9757941000007122</v>
+      </c>
+      <c r="I3">
+        <v>0.16760740000063379</v>
+      </c>
+      <c r="J3">
+        <v>3.143401500001346</v>
+      </c>
+      <c r="K3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>50000</v>
+      </c>
+      <c r="B4">
+        <v>0.99</v>
+      </c>
+      <c r="C4">
+        <v>1000</v>
+      </c>
+      <c r="D4">
+        <v>500</v>
+      </c>
+      <c r="E4">
+        <v>1658.833333333333</v>
+      </c>
+      <c r="F4">
+        <v>964.66666666666674</v>
+      </c>
+      <c r="G4">
+        <v>125.4444444444445</v>
+      </c>
+      <c r="H4">
+        <v>3.0390098000007129</v>
+      </c>
+      <c r="I4">
+        <v>0.2137996000001294</v>
+      </c>
+      <c r="J4">
+        <v>3.2528094000008418</v>
+      </c>
+      <c r="K4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>50000</v>
+      </c>
+      <c r="B5">
+        <v>0.99</v>
+      </c>
+      <c r="C5">
+        <v>1000</v>
+      </c>
+      <c r="D5">
+        <v>1000</v>
+      </c>
+      <c r="E5">
+        <v>2465.0277777777769</v>
+      </c>
+      <c r="F5">
+        <v>1062.1111111111111</v>
+      </c>
+      <c r="G5">
+        <v>137.2777777777778</v>
+      </c>
+      <c r="H5">
+        <v>3.0441365999995469</v>
+      </c>
+      <c r="I5">
+        <v>0.15568600000005969</v>
+      </c>
+      <c r="J5">
+        <v>3.1998225999996071</v>
+      </c>
+      <c r="K5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>50000</v>
+      </c>
+      <c r="B6">
+        <v>0.99</v>
+      </c>
+      <c r="C6">
+        <v>1000</v>
+      </c>
+      <c r="D6">
+        <v>2000</v>
+      </c>
+      <c r="E6">
+        <v>2499.9722222222231</v>
+      </c>
+      <c r="F6">
+        <v>1026.9444444444439</v>
+      </c>
+      <c r="G6">
+        <v>134</v>
+      </c>
+      <c r="H6">
+        <v>3.1026521999992842</v>
+      </c>
+      <c r="I6">
+        <v>0.2828334999994695</v>
+      </c>
+      <c r="J6">
+        <v>3.3854856999987528</v>
+      </c>
+      <c r="K6">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="26.109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -434,229 +1393,183 @@
       <c r="J1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2">
+        <v>50000</v>
+      </c>
+      <c r="B2">
+        <v>0.99</v>
+      </c>
+      <c r="C2">
+        <v>1000</v>
+      </c>
+      <c r="D2">
+        <v>1000</v>
+      </c>
+      <c r="E2">
+        <v>2109.6111111111109</v>
+      </c>
+      <c r="F2">
+        <v>660.02777777777737</v>
+      </c>
+      <c r="G2">
+        <v>85.138888888888843</v>
+      </c>
+      <c r="H2">
+        <v>3.0413733999994288</v>
+      </c>
+      <c r="I2">
+        <v>0.29328389999864157</v>
+      </c>
+      <c r="J2">
+        <v>3.3346572999980708</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>50000</v>
+      </c>
+      <c r="B3">
+        <v>0.99</v>
+      </c>
+      <c r="C3">
+        <v>1000</v>
+      </c>
+      <c r="D3">
+        <v>1000</v>
+      </c>
+      <c r="E3">
+        <v>2465.0277777777769</v>
+      </c>
+      <c r="F3">
+        <v>1062.1111111111111</v>
+      </c>
+      <c r="G3">
+        <v>137.2777777777778</v>
+      </c>
+      <c r="H3">
+        <v>3.0448458999999271</v>
+      </c>
+      <c r="I3">
+        <v>0.1509232000007614</v>
+      </c>
+      <c r="J3">
+        <v>3.1957691000006889</v>
+      </c>
+      <c r="K3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>50000</v>
+      </c>
+      <c r="B4">
+        <v>0.99</v>
+      </c>
+      <c r="C4">
+        <v>1000</v>
+      </c>
+      <c r="D4">
+        <v>1000</v>
+      </c>
+      <c r="E4">
+        <v>2433.6944444444439</v>
+      </c>
+      <c r="F4">
+        <v>1401.4722222222219</v>
+      </c>
+      <c r="G4">
+        <v>164.1944444444444</v>
+      </c>
+      <c r="H4">
+        <v>3.0601872000006551</v>
+      </c>
+      <c r="I4">
+        <v>0.17589559999942139</v>
+      </c>
+      <c r="J4">
+        <v>3.236082800000077</v>
+      </c>
+      <c r="K4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>50000</v>
+      </c>
+      <c r="B5">
+        <v>0.99</v>
+      </c>
+      <c r="C5">
+        <v>1000</v>
+      </c>
+      <c r="D5">
+        <v>1000</v>
+      </c>
+      <c r="E5">
+        <v>2201.5277777777778</v>
+      </c>
+      <c r="F5">
+        <v>1371.194444444445</v>
+      </c>
+      <c r="G5">
+        <v>151.83333333333329</v>
+      </c>
+      <c r="H5">
+        <v>3.0457661000000371</v>
+      </c>
+      <c r="I5">
+        <v>0.198924000000261</v>
+      </c>
+      <c r="J5">
+        <v>3.2446901000002981</v>
+      </c>
+      <c r="K5">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>50000</v>
+      </c>
+      <c r="B6">
+        <v>0.99</v>
+      </c>
+      <c r="C6">
+        <v>1000</v>
+      </c>
+      <c r="D6">
+        <v>1000</v>
+      </c>
+      <c r="E6">
+        <v>2561.3611111111109</v>
+      </c>
+      <c r="F6">
+        <v>985.13888888888914</v>
+      </c>
+      <c r="G6">
+        <v>118.2222222222222</v>
+      </c>
+      <c r="H6">
+        <v>3.0794798000006272</v>
+      </c>
+      <c r="I6">
+        <v>0.2356318999991345</v>
+      </c>
+      <c r="J6">
+        <v>3.3151116999997612</v>
+      </c>
+      <c r="K6">
         <v>100</v>
-      </c>
-      <c r="B2">
-        <v>0.99</v>
-      </c>
-      <c r="C2">
-        <v>1000</v>
-      </c>
-      <c r="D2">
-        <v>1000</v>
-      </c>
-      <c r="E2">
-        <v>4182.75</v>
-      </c>
-      <c r="F2">
-        <v>1411.583333333333</v>
-      </c>
-      <c r="G2">
-        <v>157.6944444444444</v>
-      </c>
-      <c r="H2">
-        <v>8.616200000687968E-3</v>
-      </c>
-      <c r="I2">
-        <v>0.58612530000027618</v>
-      </c>
-      <c r="J2">
-        <v>0.59474150000096415</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>500</v>
-      </c>
-      <c r="B3">
-        <v>0.99</v>
-      </c>
-      <c r="C3">
-        <v>1000</v>
-      </c>
-      <c r="D3">
-        <v>1000</v>
-      </c>
-      <c r="E3">
-        <v>3681.8055555555561</v>
-      </c>
-      <c r="F3">
-        <v>1328.1388888888889</v>
-      </c>
-      <c r="G3">
-        <v>165.19444444444451</v>
-      </c>
-      <c r="H3">
-        <v>4.0386799999396317E-2</v>
-      </c>
-      <c r="I3">
-        <v>0.65414980000059586</v>
-      </c>
-      <c r="J3">
-        <v>0.69453659999999218</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>1000</v>
-      </c>
-      <c r="B4">
-        <v>0.99</v>
-      </c>
-      <c r="C4">
-        <v>1000</v>
-      </c>
-      <c r="D4">
-        <v>1000</v>
-      </c>
-      <c r="E4">
-        <v>3681.8055555555561</v>
-      </c>
-      <c r="F4">
-        <v>1328.1388888888889</v>
-      </c>
-      <c r="G4">
-        <v>165.19444444444451</v>
-      </c>
-      <c r="H4">
-        <v>7.582649999858404E-2</v>
-      </c>
-      <c r="I4">
-        <v>0.6134382000000187</v>
-      </c>
-      <c r="J4">
-        <v>0.68926469999860274</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>5000</v>
-      </c>
-      <c r="B5">
-        <v>0.99</v>
-      </c>
-      <c r="C5">
-        <v>1000</v>
-      </c>
-      <c r="D5">
-        <v>1000</v>
-      </c>
-      <c r="E5">
-        <v>3464.166666666667</v>
-      </c>
-      <c r="F5">
-        <v>1145.833333333333</v>
-      </c>
-      <c r="G5">
-        <v>122.3888888888889</v>
-      </c>
-      <c r="H5">
-        <v>0.4149942000003648</v>
-      </c>
-      <c r="I5">
-        <v>0.32653629999913392</v>
-      </c>
-      <c r="J5">
-        <v>0.74153049999949872</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>10000</v>
-      </c>
-      <c r="B6">
-        <v>0.99</v>
-      </c>
-      <c r="C6">
-        <v>1000</v>
-      </c>
-      <c r="D6">
-        <v>1000</v>
-      </c>
-      <c r="E6">
-        <v>2963.3611111111109</v>
-      </c>
-      <c r="F6">
-        <v>1001.6666666666659</v>
-      </c>
-      <c r="G6">
-        <v>118.6944444444444</v>
-      </c>
-      <c r="H6">
-        <v>0.81369600000107312</v>
-      </c>
-      <c r="I6">
-        <v>0.45495010000013281</v>
-      </c>
-      <c r="J6">
-        <v>1.2686461000012059</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>50000</v>
-      </c>
-      <c r="B7">
-        <v>0.99</v>
-      </c>
-      <c r="C7">
-        <v>1000</v>
-      </c>
-      <c r="D7">
-        <v>1000</v>
-      </c>
-      <c r="E7">
-        <v>2465.0277777777769</v>
-      </c>
-      <c r="F7">
-        <v>1062.1111111111111</v>
-      </c>
-      <c r="G7">
-        <v>137.2777777777778</v>
-      </c>
-      <c r="H7">
-        <v>4.0976073000001634</v>
-      </c>
-      <c r="I7">
-        <v>0.19047420000060811</v>
-      </c>
-      <c r="J7">
-        <v>4.2880815000007706</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>1000000</v>
-      </c>
-      <c r="B8">
-        <v>0.99</v>
-      </c>
-      <c r="C8">
-        <v>1000</v>
-      </c>
-      <c r="D8">
-        <v>1000</v>
-      </c>
-      <c r="E8">
-        <v>301.77777777777783</v>
-      </c>
-      <c r="F8">
-        <v>301.77777777777783</v>
-      </c>
-      <c r="G8">
-        <v>47.333333333333343</v>
-      </c>
-      <c r="H8">
-        <v>78.299767699998483</v>
-      </c>
-      <c r="I8">
-        <v>3.8325099998473888E-2</v>
-      </c>
-      <c r="J8">
-        <v>78.338092799996957</v>
       </c>
     </row>
   </sheetData>

--- a/Experimenten.xlsx
+++ b/Experimenten.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stichtingfontys-my.sharepoint.com/personal/582755_student_fontys_nl/Documents/Leerjaar 2/Periode 1/Operations Research 5/OR5/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_95EC686F11BDBA4E79E2DE4F4CDD18D428DF8E2A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3191706-C65E-43E3-A992-83E92E14118B}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_95EC686F11BDBA4E79E2DE4F4CDD18D428DF8E2A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A4BE203-74C6-4194-A5DC-73B539CAF03C}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-48" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="t_max" sheetId="1" r:id="rId1"/>
@@ -398,6 +398,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -1128,6 +1141,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">

--- a/Experimenten.xlsx
+++ b/Experimenten.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stichtingfontys-my.sharepoint.com/personal/582755_student_fontys_nl/Documents/Leerjaar 2/Periode 1/Operations Research 5/OR5/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="11_E1A8E876E44D7F44EB205E5B54E1B21826485FC6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48F99BC6-7E0E-4DF2-9795-46F891442EAD}"/>
+  <xr:revisionPtr revIDLastSave="72" documentId="11_E1A8E876E44D7F44EB205E5B54E1B21826485FC6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9AFB4758-D5B2-4F1C-B3FC-FDE4D9A4E4C6}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="25032" yWindow="1704" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="t_max" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="13">
   <si>
     <t>t_max</t>
   </si>
@@ -57,6 +57,12 @@
   </si>
   <si>
     <t>Random seed</t>
+  </si>
+  <si>
+    <t>Penalty Simulated Annealing</t>
+  </si>
+  <si>
+    <t>Penalty na improving search</t>
   </si>
 </sst>
 </file>
@@ -109,6 +115,2566 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="50000"/>
+                    <a:lumOff val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mj-lt"/>
+                <a:ea typeface="+mj-ea"/>
+                <a:cs typeface="+mj-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="nl-NL"/>
+              <a:t>Invloed van het aantal iteraties op de total penalty</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="9.193202173229173E-2"/>
+          <c:y val="0"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="50000"/>
+                  <a:lumOff val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mj-lt"/>
+              <a:ea typeface="+mj-ea"/>
+              <a:cs typeface="+mj-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="nl-NL"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.10978790646763868"/>
+          <c:y val="0.12697788697788698"/>
+          <c:w val="0.84330068873549402"/>
+          <c:h val="0.65661449566961383"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>t_max!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Penalty Simulated Annealing</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="9525" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:alpha val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="diamond"/>
+            <c:size val="6"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:ln w="15875">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>t_max!$A$2:$A$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>50000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>500000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1000000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>t_max!$E$2:$E$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>4024.8888888888891</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3380.416666666667</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3380.416666666667</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3111.8888888888878</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2342.555555555557</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2109.6111111111109</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>187.63888888888891</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>187.63888888888891</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-510E-4C69-9F33-36CBFAC42B0E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>t_max!$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Penalty na improving search</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="9525" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:alpha val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="square"/>
+            <c:size val="6"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:ln w="15875">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>t_max!$A$2:$A$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>50000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>500000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1000000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>t_max!$F$2:$F$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>1071.7222222222219</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1229.4444444444439</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1229.4444444444439</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>571.11111111111131</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>923.77777777777794</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>660.02777777777737</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>179.638888888889</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>179.638888888889</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-510E-4C69-9F33-36CBFAC42B0E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1335655440"/>
+        <c:axId val="602084592"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1335655440"/>
+        <c:scaling>
+          <c:logBase val="10"/>
+          <c:orientation val="minMax"/>
+          <c:min val="100"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="dk1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="nl-NL"/>
+                  <a:t>Number of iterations (t_max)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="nl-NL"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="low"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="dk1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+                <a:alpha val="54000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="nl-NL"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="602084592"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="602084592"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="dk1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="nl-NL"/>
+                  <a:t>Total penalty</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="nl-NL"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="dk1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+                <a:alpha val="54000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="nl-NL"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1335655440"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:pattFill prst="ltDnDiag">
+          <a:fgClr>
+            <a:schemeClr val="dk1">
+              <a:lumMod val="15000"/>
+              <a:lumOff val="85000"/>
+            </a:schemeClr>
+          </a:fgClr>
+          <a:bgClr>
+            <a:schemeClr val="lt1"/>
+          </a:bgClr>
+        </a:pattFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="nl-NL"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="lt1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="nl-NL"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="50000"/>
+                    <a:lumOff val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mj-lt"/>
+                <a:ea typeface="+mj-ea"/>
+                <a:cs typeface="+mj-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="nl-NL"/>
+              <a:t>Invloed van het aantal iteraties op de totale</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="nl-NL" baseline="0"/>
+              <a:t> penalty</a:t>
+            </a:r>
+            <a:endParaRPr lang="nl-NL"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="50000"/>
+                  <a:lumOff val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mj-lt"/>
+              <a:ea typeface="+mj-ea"/>
+              <a:cs typeface="+mj-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="nl-NL"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>t_max!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Penalty Simulated Annealing</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>t_max!$A$2:$A$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>50000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>500000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1000000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>t_max!$E$2:$E$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>4024.8888888888891</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3380.416666666667</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3380.416666666667</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3111.8888888888878</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2342.555555555557</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2109.6111111111109</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>187.63888888888891</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>187.63888888888891</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-EBC4-4FCB-B0E4-72769A5C90A7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>t_max!$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Penalty na improving search</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>t_max!$A$2:$A$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>50000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>500000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1000000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>t_max!$F$2:$F$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>1071.7222222222219</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1229.4444444444439</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1229.4444444444439</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>571.11111111111131</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>923.77777777777794</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>660.02777777777737</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>179.638888888889</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>179.638888888889</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-EBC4-4FCB-B0E4-72769A5C90A7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="267"/>
+        <c:overlap val="-43"/>
+        <c:axId val="1353656768"/>
+        <c:axId val="1420484560"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1353656768"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="dk1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="nl-NL"/>
+                  <a:t>Aantal</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="nl-NL" baseline="0"/>
+                  <a:t> iteraties (t_max)</a:t>
+                </a:r>
+                <a:endParaRPr lang="nl-NL"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="nl-NL"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="dk1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="nl-NL"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1420484560"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1420484560"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="dk1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="nl-NL"/>
+                  <a:t>Totale penalty</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="nl-NL"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="nl-NL"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1353656768"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:pattFill prst="ltDnDiag">
+          <a:fgClr>
+            <a:schemeClr val="dk1">
+              <a:lumMod val="15000"/>
+              <a:lumOff val="85000"/>
+            </a:schemeClr>
+          </a:fgClr>
+          <a:bgClr>
+            <a:schemeClr val="lt1"/>
+          </a:bgClr>
+        </a:pattFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="nl-NL"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="lt1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="nl-NL"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="250">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="15875">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="800" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="ltDnDiag">
+        <a:fgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="lt1"/>
+        </a:bgClr>
+      </a:pattFill>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="ltDnDiag">
+        <a:fgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="lt1"/>
+        </a:bgClr>
+      </a:pattFill>
+    </cs:spPr>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="major">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="ltDnDiag">
+        <a:fgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="lt1"/>
+        </a:bgClr>
+      </a:pattFill>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="208">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="22225" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="15875">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="800" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="ltDnDiag">
+        <a:fgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="lt1"/>
+        </a:bgClr>
+      </a:pattFill>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="ltDnDiag">
+        <a:fgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="lt1"/>
+        </a:bgClr>
+      </a:pattFill>
+    </cs:spPr>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="major">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="ltDnDiag">
+        <a:fgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="lt1"/>
+        </a:bgClr>
+      </a:pattFill>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>28573</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E1F811BD-DD7F-8D09-8BA7-D5B48C67154E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{76D37430-4488-A7BC-CC3F-F4CCE02B8AE8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -403,8 +2969,8 @@
     <col min="2" max="2" width="13.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="28.5703125" bestFit="1" customWidth="1"/>
@@ -426,10 +2992,10 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G1" t="s">
         <v>6</v>
@@ -729,6 +3295,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/Experimenten.xlsx
+++ b/Experimenten.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stichtingfontys-my.sharepoint.com/personal/582755_student_fontys_nl/Documents/Leerjaar 2/Periode 1/Operations Research 5/OR5/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="72" documentId="11_E1A8E876E44D7F44EB205E5B54E1B21826485FC6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9AFB4758-D5B2-4F1C-B3FC-FDE4D9A4E4C6}"/>
+  <xr:revisionPtr revIDLastSave="73" documentId="11_E1A8E876E44D7F44EB205E5B54E1B21826485FC6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{39CB30F0-1C33-45B3-9033-89D67EB5BB63}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,20 @@
     <sheet name="temp" sheetId="4" r:id="rId4"/>
     <sheet name="random_seed" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
